--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -69,7 +69,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A1001">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B1001">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="B2:B1001">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -69,7 +69,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A1001">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="B2:B1001">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="B2:B1001">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -69,7 +69,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A1001">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B1001">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="B2:B1001">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Employees">
     <column index="1" property="Age"/>
     <column index="2" property="IsActive"/>
